--- a/informes_data/Segunda FEB/2025-26/playoffs/individual/NP_play_by_play_2512402_PERMANENCIAFINAL_PROCESSED.xlsx
+++ b/informes_data/Segunda FEB/2025-26/playoffs/individual/NP_play_by_play_2512402_PERMANENCIAFINAL_PROCESSED.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. SANTA BARBARA CARCELEN</t>
+          <t>G. VERGARA HARBOE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.4579</v>
+        <v>4.9633</v>
       </c>
       <c r="E2" t="n">
-        <v>1.4858</v>
+        <v>2.5708</v>
       </c>
       <c r="F2" t="n">
-        <v>2.9721</v>
+        <v>2.3924</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.9579</v>
+        <v>2.8828</v>
       </c>
       <c r="H2" t="n">
-        <v>1.3798</v>
+        <v>0.0573</v>
       </c>
       <c r="I2" t="n">
-        <v>-2.3377</v>
+        <v>2.8255</v>
       </c>
       <c r="J2" t="n">
-        <v>-1.0492</v>
+        <v>1.8618</v>
       </c>
       <c r="K2" t="n">
-        <v>0.962</v>
+        <v>0.3529</v>
       </c>
       <c r="L2" t="n">
-        <v>-2.0112</v>
+        <v>1.5089</v>
       </c>
       <c r="M2" t="n">
-        <v>0.09130000000000001</v>
+        <v>1.0209</v>
       </c>
       <c r="N2" t="n">
-        <v>0.4178</v>
+        <v>-0.2957</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.3264</v>
+        <v>1.3166</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.4097</v>
+        <v>0.8098</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.0485</v>
+        <v>-1.0123</v>
       </c>
       <c r="R2" t="n">
-        <v>1.6388</v>
+        <v>1.8221</v>
       </c>
       <c r="S2" t="n">
-        <v>4.6449</v>
+        <v>0.0805</v>
       </c>
       <c r="T2" t="n">
-        <v>3.4029</v>
+        <v>0.2801</v>
       </c>
       <c r="U2" t="n">
-        <v>1.242</v>
+        <v>-0.1996</v>
       </c>
       <c r="V2" t="n">
-        <v>1.1806</v>
+        <v>1.1902</v>
       </c>
       <c r="W2" t="n">
-        <v>1.1806</v>
+        <v>1.4411</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-0.2509</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. MARTINEZ MEGIAS</t>
+          <t>L. FAIAL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.0541</v>
+        <v>4.1797</v>
       </c>
       <c r="E3" t="n">
-        <v>2.1698</v>
+        <v>2.4162</v>
       </c>
       <c r="F3" t="n">
-        <v>1.8843</v>
+        <v>1.7635</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9603</v>
+        <v>1.3052</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.5351</v>
+        <v>0.8296</v>
       </c>
       <c r="I3" t="n">
-        <v>1.4954</v>
+        <v>0.4756</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0458</v>
+        <v>1.0794</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.0332</v>
+        <v>1.2637</v>
       </c>
       <c r="L3" t="n">
-        <v>0.079</v>
+        <v>-0.1843</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9145</v>
+        <v>0.2258</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.5019</v>
+        <v>-0.4341</v>
       </c>
       <c r="O3" t="n">
-        <v>1.4164</v>
+        <v>0.6599</v>
       </c>
       <c r="P3" t="n">
-        <v>1.0242</v>
+        <v>0.8098</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.0123</v>
       </c>
       <c r="R3" t="n">
-        <v>1.0242</v>
+        <v>1.8221</v>
       </c>
       <c r="S3" t="n">
-        <v>2.3116</v>
+        <v>-0.3157</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9434</v>
+        <v>-0.0313</v>
       </c>
       <c r="U3" t="n">
-        <v>1.3682</v>
+        <v>-0.2843</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.2421</v>
+        <v>2.3804</v>
       </c>
       <c r="W3" t="n">
-        <v>1.1806</v>
+        <v>2.3804</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.4227</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L. FAIAL</t>
+          <t>J. MARTINEZ MEGIAS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.5435</v>
+        <v>3.1028</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5105</v>
+        <v>1.9482</v>
       </c>
       <c r="F4" t="n">
-        <v>2.0329</v>
+        <v>1.1546</v>
       </c>
       <c r="G4" t="n">
-        <v>1.2932</v>
+        <v>0.9476</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8169</v>
+        <v>-0.5338000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4763</v>
+        <v>1.4814</v>
       </c>
       <c r="J4" t="n">
-        <v>1.0167</v>
+        <v>0.0591</v>
       </c>
       <c r="K4" t="n">
-        <v>1.2352</v>
+        <v>-0.0204</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.2185</v>
+        <v>0.0795</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2765</v>
+        <v>0.8885</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4183</v>
+        <v>-0.5134</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6948</v>
+        <v>1.4019</v>
       </c>
       <c r="P4" t="n">
-        <v>0.8194</v>
+        <v>1.0123</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.0242</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8436</v>
+        <v>1.0123</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.9303</v>
+        <v>1.3939</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8431</v>
+        <v>0.6989</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0872</v>
+        <v>0.6949</v>
       </c>
       <c r="V4" t="n">
-        <v>2.3612</v>
+        <v>-0.2509</v>
       </c>
       <c r="W4" t="n">
-        <v>2.3612</v>
+        <v>1.1902</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.4411</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. VERGARA HARBOE</t>
+          <t>F. LOPEZ JIMENEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.4991</v>
+        <v>2.8265</v>
       </c>
       <c r="E5" t="n">
-        <v>1.3073</v>
+        <v>1.5958</v>
       </c>
       <c r="F5" t="n">
-        <v>2.1918</v>
+        <v>1.2307</v>
       </c>
       <c r="G5" t="n">
-        <v>2.8187</v>
+        <v>0.7118</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0174</v>
+        <v>0.5734</v>
       </c>
       <c r="I5" t="n">
-        <v>2.8014</v>
+        <v>0.1384</v>
       </c>
       <c r="J5" t="n">
-        <v>1.752</v>
+        <v>0.0198</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2964</v>
+        <v>0.0198</v>
       </c>
       <c r="L5" t="n">
-        <v>1.4556</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1.0668</v>
+        <v>0.6921</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.279</v>
+        <v>0.5537</v>
       </c>
       <c r="O5" t="n">
-        <v>1.3458</v>
+        <v>0.1384</v>
       </c>
       <c r="P5" t="n">
-        <v>0.8194</v>
+        <v>0.4049</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0242</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8436</v>
+        <v>0.4049</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.3197</v>
+        <v>0.5195</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8431</v>
+        <v>0.3858</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4765</v>
+        <v>0.1337</v>
       </c>
       <c r="V5" t="n">
-        <v>1.1806</v>
+        <v>1.1902</v>
       </c>
       <c r="W5" t="n">
-        <v>1.4227</v>
+        <v>1.1902</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>F. LOPEZ JIMENEZ</t>
+          <t>J. SANTA BARBARA CARCELEN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.5489</v>
+        <v>1.7907</v>
       </c>
       <c r="E6" t="n">
-        <v>1.274</v>
+        <v>-0.5655</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2749</v>
+        <v>2.3562</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7163</v>
+        <v>-0.9577</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5769</v>
+        <v>1.3835</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1394</v>
+        <v>-2.3412</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0195</v>
+        <v>-1.0097</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0195</v>
+        <v>0.9871</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-1.9968</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6968</v>
+        <v>0.052</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5574</v>
+        <v>0.3964</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1394</v>
+        <v>-0.3444</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4097</v>
+        <v>-0.4049</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.0245</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4097</v>
+        <v>1.6196</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2423</v>
+        <v>1.9631</v>
       </c>
       <c r="T6" t="n">
-        <v>0.07389999999999999</v>
+        <v>1.2785</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1685</v>
+        <v>0.6846</v>
       </c>
       <c r="V6" t="n">
-        <v>1.1806</v>
+        <v>1.1902</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1806</v>
+        <v>1.1902</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1033</v>
+        <v>0.6401</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3247</v>
+        <v>0.5794</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2214</v>
+        <v>0.0607</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2276</v>
+        <v>0.2387</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6855</v>
+        <v>-0.6727</v>
       </c>
       <c r="I7" t="n">
-        <v>0.913</v>
+        <v>0.9115</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0527</v>
+        <v>0.1074</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.49</v>
+        <v>-0.4564</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5427</v>
+        <v>0.5638</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1749</v>
+        <v>0.1313</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1954</v>
+        <v>-0.2164</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3703</v>
+        <v>0.3477</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R7" t="n">
-        <v>1.0242</v>
+        <v>1.0123</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7146</v>
+        <v>-0.1937</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1156</v>
+        <v>0.294</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.8302</v>
+        <v>-0.4877</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5903</v>
+        <v>0.5951</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1806</v>
+        <v>1.1902</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5903</v>
+        <v>-0.5951</v>
       </c>
     </row>
     <row r="8">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4494</v>
+        <v>-0.6014</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.2404</v>
+        <v>-1.422</v>
       </c>
       <c r="F8" t="n">
-        <v>0.791</v>
+        <v>0.8207</v>
       </c>
       <c r="G8" t="n">
-        <v>1.2585</v>
+        <v>1.2442</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3205</v>
+        <v>0.3165</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.9277</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1766</v>
+        <v>0.1783</v>
       </c>
       <c r="K8" t="n">
-        <v>0.09760000000000001</v>
+        <v>0.0988</v>
       </c>
       <c r="L8" t="n">
-        <v>0.079</v>
+        <v>0.0795</v>
       </c>
       <c r="M8" t="n">
-        <v>1.0819</v>
+        <v>1.0659</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2229</v>
+        <v>0.2177</v>
       </c>
       <c r="O8" t="n">
-        <v>0.859</v>
+        <v>0.8482</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R8" t="n">
-        <v>1.0242</v>
+        <v>1.0123</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2853</v>
+        <v>-0.4044</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3038</v>
+        <v>0.1003</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.589</v>
+        <v>-0.5047</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.4227</v>
+        <v>-1.4411</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.6965</v>
+        <v>-0.6883</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.7262</v>
+        <v>-0.7528</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>K. FELIZOR</t>
+          <t>A. LOPES MARQUES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.1266</v>
+        <v>-1.0659</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.1437</v>
+        <v>-1.0237</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0172</v>
+        <v>-0.0421</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.1017</v>
+        <v>0.7138</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4068</v>
+        <v>-0.0195</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.695</v>
+        <v>0.7333</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.6537</v>
+        <v>1.9076</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.3787</v>
+        <v>-0.0007</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.275</v>
+        <v>1.9082</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.448</v>
+        <v>-1.1938</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.028</v>
+        <v>-0.0188</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.42</v>
+        <v>-1.1749</v>
       </c>
       <c r="P9" t="n">
-        <v>1.4339</v>
+        <v>-2.227</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-3.0368</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4339</v>
+        <v>0.8098</v>
       </c>
       <c r="S9" t="n">
-        <v>1.5245</v>
+        <v>0.4473</v>
       </c>
       <c r="T9" t="n">
-        <v>1.3127</v>
+        <v>0.1054</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2119</v>
+        <v>0.3418</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.9833</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.8027</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.1806</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. LOPES MARQUES</t>
+          <t>I. CASAS GARRIDO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.8607</v>
+        <v>-1.4854</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.5744</v>
+        <v>-0.2402</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2863</v>
+        <v>-1.2452</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7202</v>
+        <v>-2.3239</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.014</v>
+        <v>0.9685</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7342</v>
+        <v>-3.2924</v>
       </c>
       <c r="J10" t="n">
-        <v>1.883</v>
+        <v>-0.9893</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.0137</v>
+        <v>1.0075</v>
       </c>
       <c r="L10" t="n">
-        <v>1.8967</v>
+        <v>-1.9968</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.1628</v>
+        <v>-1.3346</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0003</v>
+        <v>-0.039</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.1625</v>
+        <v>-1.2957</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.2533</v>
+        <v>1.0123</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.0727</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.8194</v>
+        <v>1.0123</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3275</v>
+        <v>0.1704</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3846</v>
+        <v>-0.097</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0571</v>
+        <v>0.2674</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.3442</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.846</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>I. CASAS GARRIDO</t>
+          <t>K. FELIZOR</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.8995</v>
+        <v>-1.8531</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.7731</v>
+        <v>-1.7876</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1264</v>
+        <v>-0.0655</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.323</v>
+        <v>-2.1083</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9671999999999999</v>
+        <v>-0.3959</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.2902</v>
+        <v>-1.7124</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.016</v>
+        <v>-1.6218</v>
       </c>
       <c r="K11" t="n">
-        <v>0.9953</v>
+        <v>-0.3569</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.0112</v>
+        <v>-1.2649</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.307</v>
+        <v>-0.4864</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.028</v>
+        <v>-0.039</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.279</v>
+        <v>-0.4474</v>
       </c>
       <c r="P11" t="n">
-        <v>1.0242</v>
+        <v>1.4172</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.0242</v>
+        <v>1.4172</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2525</v>
+        <v>0.8098</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5895</v>
+        <v>0.6158</v>
       </c>
       <c r="U11" t="n">
-        <v>0.337</v>
+        <v>0.194</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.3482</v>
+        <v>-1.9718</v>
       </c>
       <c r="W11" t="n">
-        <v>0.8324</v>
+        <v>-0.7816</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.1806</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.9641</v>
+        <v>-2.1772</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.4124</v>
+        <v>-0.7092000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.5517</v>
+        <v>-1.468</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.599</v>
+        <v>-1.628</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.973</v>
+        <v>-0.9876</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.626</v>
+        <v>-0.6404</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1771</v>
+        <v>0.1785</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0585</v>
+        <v>0.0593</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1185</v>
+        <v>0.1193</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.776</v>
+        <v>-1.8066</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.0316</v>
+        <v>-1.0469</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.7445000000000001</v>
+        <v>-0.7597</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.2048</v>
+        <v>-0.2025</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R12" t="n">
-        <v>0.8194</v>
+        <v>0.8098</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0244</v>
+        <v>-0.189</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4348</v>
+        <v>0.1245</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4592</v>
+        <v>-0.3136</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.1359</v>
+        <v>-0.1577</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.1359</v>
+        <v>-0.1577</v>
       </c>
     </row>
     <row r="13">
@@ -1423,58 +1423,58 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.6046</v>
+        <v>-2.3907</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.8466</v>
+        <v>-3.8062</v>
       </c>
       <c r="F13" t="n">
-        <v>1.242</v>
+        <v>1.4155</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.7826</v>
+        <v>-0.7551</v>
       </c>
       <c r="H13" t="n">
-        <v>1.3243</v>
+        <v>1.3432</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.1069</v>
+        <v>-2.0983</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.1114</v>
+        <v>-0.0322</v>
       </c>
       <c r="K13" t="n">
-        <v>1.4362</v>
+        <v>1.4803</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.5475</v>
+        <v>-1.5125</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.6712</v>
+        <v>-0.7229</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.1119</v>
+        <v>-0.1371</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.5593</v>
+        <v>-0.5859</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.663</v>
+        <v>-2.6319</v>
       </c>
       <c r="Q13" t="n">
-        <v>-4.097</v>
+        <v>-4.049</v>
       </c>
       <c r="R13" t="n">
-        <v>1.4339</v>
+        <v>1.4172</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.159</v>
+        <v>0.9962</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6383</v>
+        <v>0.2749</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4793</v>
+        <v>0.7213000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.301900000000002</v>
+        <v>7.9294</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.918499999999999</v>
+        <v>-0.4439999999999995</v>
       </c>
       <c r="F14" t="n">
-        <v>9.220400000000001</v>
+        <v>8.373499999999998</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2306000000000001</v>
+        <v>0.2710999999999996</v>
       </c>
       <c r="H14" t="n">
-        <v>2.7886</v>
+        <v>2.8625</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.5581</v>
+        <v>-2.5913</v>
       </c>
       <c r="J14" t="n">
-        <v>1.2931</v>
+        <v>1.7389</v>
       </c>
       <c r="K14" t="n">
-        <v>4.1851</v>
+        <v>4.435</v>
       </c>
       <c r="L14" t="n">
-        <v>-2.8919</v>
+        <v>-2.6961</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.0623</v>
+        <v>-1.4678</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.3963</v>
+        <v>-1.5726</v>
       </c>
       <c r="O14" t="n">
-        <v>0.3339999999999999</v>
+        <v>0.1046999999999999</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-14.3392</v>
+        <v>-14.1718</v>
       </c>
       <c r="R14" t="n">
-        <v>14.3391</v>
+        <v>14.1719</v>
       </c>
       <c r="S14" t="n">
-        <v>4.71</v>
+        <v>5.2779</v>
       </c>
       <c r="T14" t="n">
-        <v>3.288499999999999</v>
+        <v>4.0299</v>
       </c>
       <c r="U14" t="n">
-        <v>1.4219</v>
+        <v>1.2478</v>
       </c>
       <c r="V14" t="n">
-        <v>2.361100000000001</v>
+        <v>2.3804</v>
       </c>
       <c r="W14" t="n">
-        <v>7.8395</v>
+        <v>7.9584</v>
       </c>
       <c r="X14" t="n">
-        <v>-5.478400000000001</v>
+        <v>-5.578</v>
       </c>
     </row>
     <row r="15">
@@ -1579,58 +1579,58 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.4055</v>
+        <v>3.4967</v>
       </c>
       <c r="E15" t="n">
-        <v>1.5549</v>
+        <v>1.6017</v>
       </c>
       <c r="F15" t="n">
-        <v>1.8506</v>
+        <v>1.895</v>
       </c>
       <c r="G15" t="n">
-        <v>4.1303</v>
+        <v>4.1087</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.229</v>
+        <v>-0.2556</v>
       </c>
       <c r="I15" t="n">
-        <v>4.3592</v>
+        <v>4.3644</v>
       </c>
       <c r="J15" t="n">
-        <v>3.1602</v>
+        <v>3.1799</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0781</v>
+        <v>0.079</v>
       </c>
       <c r="L15" t="n">
-        <v>3.0822</v>
+        <v>3.1009</v>
       </c>
       <c r="M15" t="n">
-        <v>0.97</v>
+        <v>0.9288</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.307</v>
+        <v>-0.3346</v>
       </c>
       <c r="O15" t="n">
-        <v>1.2771</v>
+        <v>1.2635</v>
       </c>
       <c r="P15" t="n">
-        <v>0.4097</v>
+        <v>0.4049</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4339</v>
+        <v>1.4172</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.1345</v>
+        <v>-1.017</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5810999999999999</v>
+        <v>-0.5659</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5533</v>
+        <v>-0.451</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C. TOLEDO ZAMORA</t>
+          <t>G. CADME ARIAS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.0527</v>
+        <v>1.7964</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4334</v>
+        <v>0.8921</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6193</v>
+        <v>0.9043</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.1945</v>
+        <v>0.7943</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.3377</v>
+        <v>0.9887</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8568</v>
+        <v>-0.1944</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.2952</v>
+        <v>1.5551</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.8355</v>
+        <v>1.0075</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.4597</v>
+        <v>0.5476</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.8993</v>
+        <v>-0.7608</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5022</v>
+        <v>-0.0188</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.3971</v>
+        <v>-0.742</v>
       </c>
       <c r="P16" t="n">
-        <v>1.8436</v>
+        <v>0.4049</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.0123</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8436</v>
+        <v>1.4172</v>
       </c>
       <c r="S16" t="n">
-        <v>1.3291</v>
+        <v>0.7665</v>
       </c>
       <c r="T16" t="n">
-        <v>0.928</v>
+        <v>0.3493</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4011</v>
+        <v>0.4172</v>
       </c>
       <c r="V16" t="n">
-        <v>1.0744</v>
+        <v>-0.1692</v>
       </c>
       <c r="W16" t="n">
-        <v>1.8006</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.7262</v>
+        <v>-0.1692</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. CADME ARIAS</t>
+          <t>R. TIMONER GIMENEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.7835</v>
+        <v>1.64</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8259</v>
+        <v>0.2281</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9575</v>
+        <v>1.4118</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7911</v>
+        <v>0.0095</v>
       </c>
       <c r="H17" t="n">
-        <v>0.995</v>
+        <v>0.4558</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2039</v>
+        <v>-0.4463</v>
       </c>
       <c r="J17" t="n">
-        <v>1.513</v>
+        <v>-0.2212</v>
       </c>
       <c r="K17" t="n">
-        <v>0.9953</v>
+        <v>0.7112000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>0.5177</v>
+        <v>-0.9324</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.7219</v>
+        <v>0.2307</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0003</v>
+        <v>-0.2553</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.7216</v>
+        <v>0.4861</v>
       </c>
       <c r="P17" t="n">
-        <v>0.4097</v>
+        <v>1.0123</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4339</v>
+        <v>2.0245</v>
       </c>
       <c r="S17" t="n">
-        <v>0.7492</v>
+        <v>-0.6536999999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3372</v>
+        <v>0.0204</v>
       </c>
       <c r="U17" t="n">
-        <v>0.412</v>
+        <v>-0.6742</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.1665</v>
+        <v>1.2719</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.4411</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1665</v>
+        <v>-0.1692</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. TIMONER GIMENEZ</t>
+          <t>C. TOLEDO ZAMORA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.0788</v>
+        <v>0.9183</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1966</v>
+        <v>0.5096000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2754</v>
+        <v>0.4087</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0089</v>
+        <v>-2.2084</v>
       </c>
       <c r="H18" t="n">
-        <v>0.479</v>
+        <v>-1.3251</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4702</v>
+        <v>-0.8833</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.2773</v>
+        <v>-1.2464</v>
       </c>
       <c r="K18" t="n">
-        <v>0.7025</v>
+        <v>-0.7929</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.9798</v>
+        <v>-0.4536</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2862</v>
+        <v>-0.9619</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2235</v>
+        <v>-0.5322</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5097</v>
+        <v>-0.4297</v>
       </c>
       <c r="P18" t="n">
-        <v>1.0242</v>
+        <v>1.8221</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0242</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.0485</v>
+        <v>1.8221</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.2106</v>
+        <v>0.2076</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3178</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.8928</v>
+        <v>0.3014</v>
       </c>
       <c r="V18" t="n">
-        <v>1.2562</v>
+        <v>1.097</v>
       </c>
       <c r="W18" t="n">
-        <v>1.4227</v>
+        <v>1.8498</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1665</v>
+        <v>-0.7528</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>H. KABASELE KASONGA</t>
+          <t>G. MILADINOVIC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1704</v>
+        <v>0.4936</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.1165</v>
+        <v>-0.2096</v>
       </c>
       <c r="F19" t="n">
-        <v>1.2868</v>
+        <v>0.7032</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.3344</v>
+        <v>0.4936</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.6464</v>
+        <v>-0.1572</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3121</v>
+        <v>0.6509</v>
       </c>
       <c r="J19" t="n">
-        <v>0.332</v>
+        <v>0.0795</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1345</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1976</v>
+        <v>0.0795</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.6664</v>
+        <v>0.4141</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.7809</v>
+        <v>-0.1572</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1145</v>
+        <v>0.5714</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.2048</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.0485</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.8436</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0131</v>
+        <v>-0.6074000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0097</v>
+        <v>-0.2891</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0034</v>
+        <v>-0.3183</v>
       </c>
       <c r="V19" t="n">
-        <v>0.6965</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.5903</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.1062</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>G. MILADINOVIC</t>
+          <t>T. BOUNDI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.08019999999999999</v>
+        <v>0.0706</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.6414</v>
+        <v>0.1627</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7216</v>
+        <v>-0.0921</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5197000000000001</v>
+        <v>0.2177</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1396</v>
+        <v>-0.0591</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6593</v>
+        <v>0.2768</v>
       </c>
       <c r="J20" t="n">
-        <v>0.079</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0.079</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.4407</v>
+        <v>0.2177</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1396</v>
+        <v>-0.0591</v>
       </c>
       <c r="O20" t="n">
-        <v>0.5803</v>
+        <v>0.2768</v>
       </c>
       <c r="P20" t="n">
-        <v>0.6145</v>
+        <v>0.4049</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6145</v>
+        <v>0.4049</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0541</v>
+        <v>-0.3011</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7205</v>
+        <v>-0.0883</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3336</v>
+        <v>-0.2128</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.2509</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.2509</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.5019</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>T. BOUNDI</t>
+          <t>H. KABASELE KASONGA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0192</v>
+        <v>0.0145</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0456</v>
+        <v>-1.1295</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.06469999999999999</v>
+        <v>1.144</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2229</v>
+        <v>-0.3459</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.0558</v>
+        <v>-0.6332</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2787</v>
+        <v>0.2873</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>0.3746</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>0.1758</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>0.1988</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2229</v>
+        <v>-0.7205</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0558</v>
+        <v>-0.8090000000000001</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2787</v>
+        <v>0.0885</v>
       </c>
       <c r="P21" t="n">
-        <v>0.4097</v>
+        <v>-0.2025</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-2.0245</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4097</v>
+        <v>1.8221</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4097</v>
+        <v>-0.1255</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1965</v>
+        <v>-0.0747</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2132</v>
+        <v>-0.0508</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.2421</v>
+        <v>0.6883</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2421</v>
+        <v>0.5951</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.4841</v>
+        <v>0.09320000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.1364</v>
+        <v>-0.1803</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.5496</v>
+        <v>-0.9859</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4132</v>
+        <v>0.8056</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.5311</v>
+        <v>-0.5143</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.8889</v>
+        <v>-0.8707</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3577</v>
+        <v>0.3563</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.0319</v>
+        <v>0.0476</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0036</v>
+        <v>0.0566</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.0355</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.4993</v>
+        <v>-0.5619</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.8925</v>
+        <v>-0.9273</v>
       </c>
       <c r="O22" t="n">
-        <v>0.3932</v>
+        <v>0.3654</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.2048</v>
+        <v>-0.2025</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.0485</v>
+        <v>-2.0245</v>
       </c>
       <c r="R22" t="n">
-        <v>1.8436</v>
+        <v>1.8221</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.6566</v>
+        <v>-0.7354000000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8919</v>
+        <v>-0.4501</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7647</v>
+        <v>-0.2853</v>
       </c>
       <c r="V22" t="n">
-        <v>1.2562</v>
+        <v>1.2719</v>
       </c>
       <c r="W22" t="n">
-        <v>1.4227</v>
+        <v>1.4411</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.1665</v>
+        <v>-0.1692</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.3927</v>
+        <v>-3.5646</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.8119</v>
+        <v>-3.2757</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.5807</v>
+        <v>-0.2889</v>
       </c>
       <c r="G23" t="n">
-        <v>1.0111</v>
+        <v>1.0218</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.0058</v>
+        <v>-0.0191</v>
       </c>
       <c r="I23" t="n">
-        <v>1.0169</v>
+        <v>1.0409</v>
       </c>
       <c r="J23" t="n">
-        <v>1.6772</v>
+        <v>1.7235</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0781</v>
+        <v>0.079</v>
       </c>
       <c r="L23" t="n">
-        <v>1.5991</v>
+        <v>1.6444</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.6661</v>
+        <v>-0.7017</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.0838</v>
+        <v>-0.09810000000000001</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.5822000000000001</v>
+        <v>-0.6036</v>
       </c>
       <c r="P23" t="n">
-        <v>-4.097</v>
+        <v>-4.049</v>
       </c>
       <c r="Q23" t="n">
-        <v>-5.1212</v>
+        <v>-5.0613</v>
       </c>
       <c r="R23" t="n">
-        <v>1.0242</v>
+        <v>1.0123</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1403</v>
+        <v>-0.3682</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3679</v>
+        <v>0.0621</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.7724</v>
+        <v>-0.4303</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.1665</v>
+        <v>-0.1692</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.1665</v>
+        <v>-0.1692</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.6846</v>
+        <v>-5.1132</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.2953</v>
+        <v>-3.7509</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.3893</v>
+        <v>-1.3623</v>
       </c>
       <c r="G24" t="n">
-        <v>-4.2463</v>
+        <v>-4.2316</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.5046</v>
+        <v>-0.5135</v>
       </c>
       <c r="I24" t="n">
-        <v>-3.7417</v>
+        <v>-3.7181</v>
       </c>
       <c r="J24" t="n">
-        <v>-3.9851</v>
+        <v>-3.9324</v>
       </c>
       <c r="K24" t="n">
-        <v>0.2205</v>
+        <v>0.2364</v>
       </c>
       <c r="L24" t="n">
-        <v>-4.2055</v>
+        <v>-4.1688</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.2612</v>
+        <v>-0.2992</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.7251</v>
+        <v>-0.7499</v>
       </c>
       <c r="O24" t="n">
-        <v>0.4639</v>
+        <v>0.4507</v>
       </c>
       <c r="P24" t="n">
-        <v>1.2291</v>
+        <v>1.2147</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.2291</v>
+        <v>1.2147</v>
       </c>
       <c r="S24" t="n">
-        <v>0.6938</v>
+        <v>0.2841</v>
       </c>
       <c r="T24" t="n">
-        <v>0.6897</v>
+        <v>0.1815</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0041</v>
+        <v>0.1027</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.3612</v>
+        <v>-2.3804</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.3612</v>
+        <v>-2.3804</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.6401</v>
+        <v>-5.4769</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.4688</v>
+        <v>-2.4162</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.1713</v>
+        <v>-3.0607</v>
       </c>
       <c r="G25" t="n">
-        <v>0.3918</v>
+        <v>0.3835</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.4546</v>
+        <v>-0.4735</v>
       </c>
       <c r="I25" t="n">
-        <v>0.8464</v>
+        <v>0.8569</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.1095</v>
+        <v>-0.09229999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>0.0195</v>
+        <v>0.0198</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.129</v>
+        <v>-0.112</v>
       </c>
       <c r="M25" t="n">
-        <v>0.5013</v>
+        <v>0.4757</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.4741</v>
+        <v>-0.4932</v>
       </c>
       <c r="O25" t="n">
-        <v>0.9755</v>
+        <v>0.9689</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.4339</v>
+        <v>-1.4172</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.0485</v>
+        <v>-2.0245</v>
       </c>
       <c r="R25" t="n">
-        <v>0.6145</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.8895999999999999</v>
+        <v>-0.7034</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.3108</v>
+        <v>-0.2995</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.5789</v>
+        <v>-0.4039</v>
       </c>
       <c r="V25" t="n">
-        <v>-3.7083</v>
+        <v>-3.7398</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-3.7083</v>
+        <v>-3.7398</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-7.301900000000001</v>
+        <v>-5.9049</v>
       </c>
       <c r="E26" t="n">
-        <v>-9.2203</v>
+        <v>-8.3736</v>
       </c>
       <c r="F26" t="n">
-        <v>1.918399999999999</v>
+        <v>2.468599999999999</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.2304999999999992</v>
+        <v>-0.2711000000000003</v>
       </c>
       <c r="H26" t="n">
-        <v>-2.7884</v>
+        <v>-2.8625</v>
       </c>
       <c r="I26" t="n">
-        <v>2.557700000000001</v>
+        <v>2.591399999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>1.0624</v>
+        <v>1.4679</v>
       </c>
       <c r="K26" t="n">
-        <v>1.3966</v>
+        <v>1.5724</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.3339000000000003</v>
+        <v>-0.1046000000000004</v>
       </c>
       <c r="M26" t="n">
-        <v>-1.2931</v>
+        <v>-1.739</v>
       </c>
       <c r="N26" t="n">
-        <v>-4.1848</v>
+        <v>-4.434699999999999</v>
       </c>
       <c r="O26" t="n">
-        <v>2.891999999999999</v>
+        <v>2.696</v>
       </c>
       <c r="P26" t="n">
-        <v>-2.220446049250313e-16</v>
+        <v>-4.440892098500626e-16</v>
       </c>
       <c r="Q26" t="n">
-        <v>-14.3393</v>
+        <v>-14.1717</v>
       </c>
       <c r="R26" t="n">
-        <v>14.3391</v>
+        <v>14.1719</v>
       </c>
       <c r="S26" t="n">
-        <v>-4.7102</v>
+        <v>-3.2535</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.4219</v>
+        <v>-1.248</v>
       </c>
       <c r="U26" t="n">
-        <v>-3.2883</v>
+        <v>-2.0053</v>
       </c>
       <c r="V26" t="n">
-        <v>-2.3613</v>
+        <v>-2.3804</v>
       </c>
       <c r="W26" t="n">
-        <v>5.478400000000001</v>
+        <v>5.578</v>
       </c>
       <c r="X26" t="n">
-        <v>-7.839600000000001</v>
+        <v>-7.9585</v>
       </c>
     </row>
   </sheetData>
